--- a/tests/TC-02/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-02/results/timetable_all_departments_even.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CSE_2_A" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CSE_2_B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="_META" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$4:$C$6</definedName>
@@ -56,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +84,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F0F0F0"/>
         <bgColor rgb="00F0F0F0"/>
       </patternFill>
@@ -100,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -114,11 +121,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,13 +161,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,9 +180,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -605,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -795,8 +841,13 @@
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="n"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
@@ -870,10 +921,15 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -907,10 +963,15 @@
       </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="11" t="n"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
@@ -934,45 +995,106 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>B1-ASD152</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Visual Design</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>B1-CS154</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Introduction to Data Analytics</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E6:H6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -984,7 +1106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1174,8 +1296,13 @@
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
+      <c r="K3" s="11" t="n"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
@@ -1249,10 +1376,15 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="n"/>
+      <c r="I5" s="12" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -1286,10 +1418,15 @@
       </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="11" t="n"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
@@ -1313,41 +1450,590 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Room Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>B1-ASD152</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Visual Design</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>B1-CS154</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Introduction to Data Analytics</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>3-1-0-0-2</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="E6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>start_col</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>end_col</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>faculty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CS154</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dr. Sandesh P</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ASD152</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dr. Abdul Wahid</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CS154</t>
         </is>
       </c>
     </row>

--- a/tests/TC-02/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-02/results/timetable_all_departments_even.xlsx
@@ -137,14 +137,14 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -841,13 +841,8 @@
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
@@ -895,9 +890,14 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="12" t="n"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
@@ -921,15 +921,10 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -939,9 +934,14 @@
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="12" t="n"/>
       <c r="S5" s="8" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
@@ -963,15 +963,10 @@
       </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="11" t="n"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
@@ -981,7 +976,12 @@
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
     </row>
@@ -1085,15 +1085,14 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E6:H6"/>
+  <mergeCells count="2">
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="P4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1296,13 +1295,8 @@
       <c r="G3" s="8" t="inlineStr"/>
       <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>B1
-TUT</t>
-        </is>
-      </c>
-      <c r="K3" s="11" t="n"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
       <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
@@ -1350,9 +1344,14 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="12" t="n"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
@@ -1376,15 +1375,10 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -1394,9 +1388,14 @@
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>B1
+LEC</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="n"/>
+      <c r="R5" s="12" t="n"/>
       <c r="S5" s="8" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
@@ -1418,15 +1417,10 @@
       </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>B1
-LEC</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="11" t="n"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
@@ -1436,7 +1430,12 @@
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>B1
+TUT</t>
+        </is>
+      </c>
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
@@ -1512,7 +1511,7 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1540,15 +1539,14 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E6:H6"/>
+  <mergeCells count="2">
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="P4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1612,13 +1610,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1627,12 +1625,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1648,13 +1646,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1663,12 +1661,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1687,10 +1685,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1699,7 +1697,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1723,10 +1721,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1735,7 +1733,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1759,10 +1757,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1776,7 +1774,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1795,10 +1793,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1812,7 +1810,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1828,13 +1826,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1843,12 +1841,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1864,13 +1862,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1879,12 +1877,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1903,10 +1901,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1915,7 +1913,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1939,10 +1937,10 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1951,7 +1949,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1975,10 +1973,10 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1992,7 +1990,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2011,10 +2009,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -2028,7 +2026,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
